--- a/Table_S2.xlsx
+++ b/Table_S2.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S2_HSF_lost" sheetId="1" r:id="Re8fc9f71ceff4526"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S2_HSF_lost" sheetId="1" r:id="Ra481d69ed13544ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -357,10 +357,8 @@
           <x:t xml:space="preserve">Native best relative score</x:t>
         </x:is>
       </x:c>
-      <x:c r="D2" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mutated best relative score</x:t>
-        </x:is>
+      <x:c r="D2" s="10" t="str">
+        <x:v>Designed HSE-disrupted best relative score</x:v>
       </x:c>
       <x:c r="E2" s="10" t="inlineStr">
         <x:is>
